--- a/Sources/raw_sales_export.xlsx
+++ b/Sources/raw_sales_export.xlsx
@@ -620,7 +620,6 @@
           <t>2 Jan 2024</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>cust4</t>
@@ -669,8 +668,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>a. khoury</t>
@@ -743,7 +740,6 @@
           <t>€2.300,00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>C. Mendes</t>
@@ -897,7 +893,6 @@
           <t>01/06/2024</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>北京商贸</t>
@@ -943,7 +938,6 @@
           <t>49.99</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>a. khoury</t>
@@ -961,7 +955,6 @@
           <t>7 Jan 2024</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>北京商贸</t>
@@ -1015,8 +1008,6 @@
           <t>8 Jan 2024</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Globex Corp</t>
@@ -1058,7 +1049,6 @@
       <c r="M12" t="n">
         <v>0.2</v>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -1132,7 +1122,6 @@
           <t>10/01/2024</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Acme Retail</t>
@@ -1196,7 +1185,6 @@
           <t>2024-01-11 00:00:00</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>cust8</t>
@@ -1250,7 +1238,6 @@
           <t>$</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1316,7 +1303,6 @@
           <t>$1,234.50</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>a. khoury</t>
@@ -1380,7 +1366,6 @@
           <t>1,000.00</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>a. khoury</t>
@@ -1398,7 +1383,6 @@
           <t>2024-01-14</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>SoluÃ§Ãµes Norte</t>
@@ -1437,7 +1421,6 @@
           <t>12.00</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1450,8 +1433,6 @@
           <t>01/15/2024</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>Müller GmbH</t>
@@ -1522,8 +1503,6 @@
           <t>01/15/2024</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>Müller GmbH</t>
@@ -1654,7 +1633,6 @@
           <t>49.99</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>a. khoury</t>
@@ -1803,7 +1781,6 @@
           <t>2024-01-19</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Soluções Norte</t>
@@ -1840,9 +1817,6 @@
       <c r="L24" t="n">
         <v>249</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>a. khoury</t>
@@ -1906,7 +1880,6 @@
           <t>€2.300,00</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>a. khoury</t>
@@ -1970,7 +1943,6 @@
           <t>999.00</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>a. khoury</t>
@@ -1988,7 +1960,6 @@
           <t>01/21/2024</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Müller GmbH</t>
@@ -2029,7 +2000,6 @@
           <t>$1,234.50</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -2047,7 +2017,6 @@
           <t>01/22/2024</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>1001</t>
@@ -2111,7 +2080,6 @@
           <t>2024-01-23</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>1006</t>
@@ -2156,7 +2124,6 @@
       <c r="N29" t="n">
         <v>980</v>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Brian  Lee</t>
@@ -2244,7 +2211,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>25/01/2024</t>
+          <t>01/25/2024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2303,7 +2270,6 @@
           <t>€2.300,00</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2313,7 +2279,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>26/01/2024</t>
+          <t>01/26/2024</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2364,7 +2330,6 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2438,7 +2403,6 @@
       <c r="B34" t="n">
         <v>45320</v>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>CafÃ© Ã–lsson</t>
@@ -2482,7 +2446,6 @@
           <t>1234.5</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>C. Mendes</t>
@@ -2543,7 +2506,6 @@
       <c r="N35" t="n">
         <v>980</v>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>C. Mendes</t>
@@ -2561,7 +2523,6 @@
           <t>01/02/2024</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
           <t>cust9</t>
@@ -2609,8 +2570,6 @@
       <c r="N36" t="n">
         <v>980</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2623,7 +2582,6 @@
           <t>01/03/2024</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>Acme Retail</t>
@@ -2668,7 +2626,6 @@
           <t>49.99</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -2687,8 +2644,6 @@
           <t>2024-01-04 00:00:00</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>Zen Trading</t>
@@ -2752,7 +2707,6 @@
           <t>01/05/2024</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>cust5</t>
@@ -2801,7 +2755,6 @@
           <t>10%</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>C. Mendes</t>
@@ -2819,7 +2772,6 @@
           <t>2024-01-06</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>1004</t>
@@ -2932,7 +2884,6 @@
       <c r="N42" t="n">
         <v>980</v>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Brian Lee</t>
@@ -2950,7 +2901,6 @@
           <t>8 Jan 2024</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Globex Corp</t>
@@ -3012,7 +2962,6 @@
           <t>09/01/2024</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>MÃ¼ller GmbH</t>
@@ -3204,7 +3153,6 @@
           <t>1,000.00</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3326,8 +3274,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Brian Lee</t>
@@ -3343,8 +3289,6 @@
       <c r="B49" t="n">
         <v>45306</v>
       </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>Acme Retail</t>
@@ -3516,7 +3460,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Brian Lee</t>
@@ -3531,7 +3474,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>17/01/2024</t>
+          <t>01/17/2024</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3599,7 +3542,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>18/01/2024</t>
+          <t>01/18/2024</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3670,7 +3613,6 @@
           <t>19 Jan 2024</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>cust1</t>
@@ -3719,8 +3661,6 @@
           <t>€2.300,00</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3782,8 +3722,6 @@
           <t>1,000.00</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3917,7 +3855,6 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3980,7 +3917,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4003,7 +3939,6 @@
           <t>2024-01-24</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>北京商贸</t>
@@ -4064,7 +3999,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>25/01/2024</t>
+          <t>01/25/2024</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4137,7 +4072,6 @@
           <t>2024-01-26 00:00:00</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t xml:space="preserve">  globex corp</t>
@@ -4186,7 +4120,6 @@
           <t>€2.300,00</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4199,7 +4132,6 @@
           <t>2024-01-27 00:00:00</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Zen Trading</t>
@@ -4241,7 +4173,6 @@
       <c r="M62" t="n">
         <v>0.1</v>
       </c>
-      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>€</t>
@@ -4328,7 +4259,6 @@
           <t>01/01/2024</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t xml:space="preserve">  globex corp</t>
@@ -4427,7 +4357,6 @@
       <c r="K65" t="n">
         <v>3</v>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>49.99</t>
@@ -4450,7 +4379,6 @@
           <t>01/03/2024</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>Müller GmbH</t>
@@ -4514,7 +4442,6 @@
           <t>04/01/2024</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>1008</t>
@@ -4563,7 +4490,6 @@
           <t>1234.5</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4574,7 +4500,6 @@
       <c r="B68" t="n">
         <v>45297</v>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>cust6</t>
@@ -4678,7 +4603,6 @@
           <t>19,99</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -4696,7 +4620,6 @@
           <t>01/07/2024</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
           <t>Soluções Norte</t>
@@ -4743,7 +4666,6 @@
           <t>1,000.00</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>C. Mendes</t>
@@ -4759,7 +4681,6 @@
       <c r="B71" t="n">
         <v>45300</v>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>MÃ¼ller GmbH</t>
@@ -4803,7 +4724,6 @@
           <t>0.15</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>C. Mendes</t>
@@ -4821,7 +4741,6 @@
           <t>2024-01-09</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>1008</t>
@@ -4865,8 +4784,6 @@
           <t>1,249.00</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>A. Khoury</t>
@@ -5000,7 +4917,6 @@
           <t>1234.5</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Brian Lee</t>
@@ -5089,7 +5005,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>13/01/2024</t>
+          <t>01/13/2024</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5130,7 +5046,6 @@
       <c r="L76" t="n">
         <v>19.99</v>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>C. Mendes</t>
@@ -5148,7 +5063,6 @@
           <t>2024-01-14</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>CUST-008</t>
@@ -5213,6 +5127,7 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>

--- a/Sources/raw_sales_export.xlsx
+++ b/Sources/raw_sales_export.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50dbc7febee0370d/Desktop/Cursor Projects/end-to-end-ETL-project/Sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_2843DDF73FAA42FEF8E283D09C4C4D95D34DE013" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C23CCE99-B309-452F-AE0F-F00255DD501C}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2843DDF73FAA42FEF8E283D09C4C4D95D34DE013" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD6264C2-D565-4A44-9CE2-84BED831CC86}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="260">
   <si>
     <t>NorthWind Global  —  Q1 2024 Sales Export</t>
   </si>
@@ -230,9 +230,6 @@
     <t>Corporate</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>49.99</t>
   </si>
   <si>
@@ -801,6 +798,9 @@
   </si>
   <si>
     <t>Contact finance-ops for questions.</t>
+  </si>
+  <si>
+    <t>1.249,00</t>
   </si>
 </sst>
 </file>
@@ -854,11 +854,11 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1170,28 +1170,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -1335,7 +1335,7 @@
       <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="2">
         <v>45294</v>
       </c>
       <c r="D7" t="s">
@@ -1358,6 +1358,9 @@
       </c>
       <c r="J7" t="s">
         <v>45</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
@@ -1404,7 +1407,7 @@
         <v>25</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L8" t="s">
         <v>57</v>
@@ -1448,7 +1451,7 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L9" t="s">
         <v>57</v>
@@ -1485,14 +1488,14 @@
       <c r="J10" t="s">
         <v>25</v>
       </c>
-      <c r="K10" t="s">
-        <v>69</v>
+      <c r="K10">
+        <v>3</v>
       </c>
       <c r="L10" t="s">
         <v>35</v>
       </c>
       <c r="N10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P10" t="s">
         <v>26</v>
@@ -1500,25 +1503,25 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
         <v>71</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
       </c>
       <c r="E11" t="s">
         <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
         <v>68</v>
       </c>
       <c r="H11" t="s">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s">
         <v>74</v>
-      </c>
-      <c r="I11" t="s">
-        <v>75</v>
       </c>
       <c r="J11" t="s">
         <v>45</v>
@@ -1530,18 +1533,18 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
         <v>77</v>
       </c>
-      <c r="B12" t="s">
+      <c r="E12" t="s">
         <v>78</v>
-      </c>
-      <c r="E12" t="s">
-        <v>79</v>
       </c>
       <c r="F12" t="s">
         <v>21</v>
@@ -1550,10 +1553,10 @@
         <v>32</v>
       </c>
       <c r="H12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" t="s">
         <v>74</v>
-      </c>
-      <c r="I12" t="s">
-        <v>75</v>
       </c>
       <c r="J12" t="s">
         <v>45</v>
@@ -1562,36 +1565,36 @@
         <v>2</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>259</v>
       </c>
       <c r="M12">
         <v>0.2</v>
       </c>
       <c r="P12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
         <v>81</v>
       </c>
-      <c r="B13" t="s">
+      <c r="E13" t="s">
         <v>82</v>
-      </c>
-      <c r="E13" t="s">
-        <v>83</v>
       </c>
       <c r="F13" t="s">
         <v>55</v>
       </c>
       <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s">
         <v>84</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>85</v>
-      </c>
-      <c r="I13" t="s">
-        <v>86</v>
       </c>
       <c r="J13" t="s">
         <v>25</v>
@@ -1608,28 +1611,28 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" t="s">
         <v>87</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
         <v>88</v>
       </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>89</v>
-      </c>
-      <c r="F14" t="s">
-        <v>90</v>
       </c>
       <c r="G14" t="s">
         <v>68</v>
       </c>
       <c r="H14" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" t="s">
         <v>91</v>
-      </c>
-      <c r="I14" t="s">
-        <v>92</v>
       </c>
       <c r="J14" t="s">
         <v>45</v>
@@ -1644,36 +1647,36 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" t="s">
         <v>94</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>95</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>96</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>97</v>
       </c>
-      <c r="F15" t="s">
-        <v>98</v>
-      </c>
       <c r="G15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" t="s">
         <v>91</v>
-      </c>
-      <c r="I15" t="s">
-        <v>92</v>
       </c>
       <c r="J15" t="s">
         <v>45</v>
@@ -1688,24 +1691,24 @@
         <v>47</v>
       </c>
       <c r="O15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
         <v>100</v>
       </c>
-      <c r="B16" t="s">
-        <v>101</v>
-      </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
         <v>39</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
         <v>31</v>
@@ -1714,13 +1717,13 @@
         <v>68</v>
       </c>
       <c r="H16" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" t="s">
         <v>103</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>104</v>
-      </c>
-      <c r="J16" t="s">
-        <v>105</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1729,7 +1732,7 @@
         <v>46</v>
       </c>
       <c r="N16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P16" t="s">
         <v>26</v>
@@ -1737,19 +1740,19 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
         <v>106</v>
       </c>
-      <c r="B17" t="s">
+      <c r="D17" t="s">
         <v>107</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G17" t="s">
         <v>42</v>
@@ -1770,7 +1773,7 @@
         <v>0.2</v>
       </c>
       <c r="N17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P17" t="s">
         <v>26</v>
@@ -1778,13 +1781,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" t="s">
         <v>110</v>
       </c>
-      <c r="B18" t="s">
+      <c r="E18" t="s">
         <v>111</v>
-      </c>
-      <c r="E18" t="s">
-        <v>112</v>
       </c>
       <c r="F18" t="s">
         <v>21</v>
@@ -1793,13 +1796,13 @@
         <v>56</v>
       </c>
       <c r="H18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I18" t="s">
         <v>24</v>
       </c>
       <c r="J18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -1810,13 +1813,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" t="s">
         <v>115</v>
       </c>
-      <c r="B19" t="s">
-        <v>116</v>
-      </c>
       <c r="E19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F19" t="s">
         <v>21</v>
@@ -1825,16 +1828,16 @@
         <v>56</v>
       </c>
       <c r="H19" t="s">
+        <v>116</v>
+      </c>
+      <c r="I19" t="s">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s">
         <v>117</v>
       </c>
-      <c r="I19" t="s">
-        <v>75</v>
-      </c>
-      <c r="J19" t="s">
-        <v>118</v>
-      </c>
-      <c r="K19" t="s">
-        <v>69</v>
+      <c r="K19">
+        <v>3</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
@@ -1843,24 +1846,24 @@
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" t="s">
         <v>115</v>
       </c>
-      <c r="B20" t="s">
-        <v>116</v>
-      </c>
       <c r="E20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F20" t="s">
         <v>21</v>
@@ -1869,16 +1872,16 @@
         <v>56</v>
       </c>
       <c r="H20" t="s">
+        <v>116</v>
+      </c>
+      <c r="I20" t="s">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s">
         <v>117</v>
       </c>
-      <c r="I20" t="s">
-        <v>75</v>
-      </c>
-      <c r="J20" t="s">
-        <v>118</v>
-      </c>
-      <c r="K20" t="s">
-        <v>69</v>
+      <c r="K20">
+        <v>2</v>
       </c>
       <c r="L20" t="s">
         <v>46</v>
@@ -1887,48 +1890,48 @@
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
         <v>120</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>121</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>122</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>123</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>124</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>125</v>
       </c>
-      <c r="G21" t="s">
-        <v>126</v>
-      </c>
       <c r="H21" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" t="s">
         <v>74</v>
-      </c>
-      <c r="I21" t="s">
-        <v>75</v>
       </c>
       <c r="J21" t="s">
         <v>45</v>
       </c>
-      <c r="K21" t="s">
-        <v>69</v>
+      <c r="K21">
+        <v>4</v>
       </c>
       <c r="L21" t="s">
         <v>57</v>
@@ -1937,7 +1940,7 @@
         <v>47</v>
       </c>
       <c r="N21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P21" t="s">
         <v>26</v>
@@ -1945,34 +1948,37 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" t="s">
         <v>127</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>128</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>129</v>
-      </c>
-      <c r="E22" t="s">
-        <v>130</v>
       </c>
       <c r="F22" t="s">
         <v>41</v>
       </c>
       <c r="G22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s">
+        <v>130</v>
+      </c>
+      <c r="I22" t="s">
         <v>131</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
+        <v>104</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+      <c r="L22" t="s">
         <v>132</v>
-      </c>
-      <c r="J22" t="s">
-        <v>105</v>
-      </c>
-      <c r="L22" t="s">
-        <v>133</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -1983,37 +1989,37 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" t="s">
         <v>134</v>
       </c>
-      <c r="B23" t="s">
-        <v>135</v>
-      </c>
       <c r="C23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D23" t="s">
         <v>39</v>
       </c>
       <c r="E23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s">
         <v>56</v>
       </c>
       <c r="H23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I23" t="s">
         <v>24</v>
       </c>
       <c r="J23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L23">
         <v>9.5</v>
@@ -2030,13 +2036,13 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
         <v>136</v>
       </c>
-      <c r="B24" t="s">
-        <v>137</v>
-      </c>
       <c r="E24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F24" t="s">
         <v>67</v>
@@ -2045,13 +2051,13 @@
         <v>56</v>
       </c>
       <c r="H24" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" t="s">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s">
         <v>117</v>
-      </c>
-      <c r="I24" t="s">
-        <v>75</v>
-      </c>
-      <c r="J24" t="s">
-        <v>118</v>
       </c>
       <c r="K24">
         <v>2</v>
@@ -2065,13 +2071,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B25">
         <v>45312</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
         <v>30</v>
@@ -2080,16 +2086,16 @@
         <v>62</v>
       </c>
       <c r="G25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H25" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I25" t="s">
         <v>24</v>
       </c>
       <c r="J25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2106,13 +2112,13 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B26">
         <v>45312</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E26" t="s">
         <v>30</v>
@@ -2121,16 +2127,16 @@
         <v>62</v>
       </c>
       <c r="G26" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I26" t="s">
         <v>24</v>
       </c>
       <c r="J26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -2139,7 +2145,7 @@
         <v>57</v>
       </c>
       <c r="N26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P26" t="s">
         <v>26</v>
@@ -2147,66 +2153,72 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" t="s">
         <v>141</v>
       </c>
-      <c r="B27" t="s">
-        <v>142</v>
-      </c>
       <c r="E27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G27" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I27" t="s">
         <v>24</v>
       </c>
       <c r="J27" t="s">
-        <v>114</v>
+        <v>113</v>
+      </c>
+      <c r="K27">
+        <v>3</v>
       </c>
       <c r="M27" t="s">
         <v>36</v>
       </c>
       <c r="N27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>142</v>
+      </c>
+      <c r="B28" t="s">
         <v>143</v>
       </c>
-      <c r="B28" t="s">
+      <c r="D28" t="s">
+        <v>112</v>
+      </c>
+      <c r="E28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" t="s">
         <v>144</v>
-      </c>
-      <c r="D28" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" t="s">
-        <v>79</v>
-      </c>
-      <c r="F28" t="s">
-        <v>145</v>
       </c>
       <c r="G28" t="s">
         <v>22</v>
       </c>
       <c r="H28" t="s">
+        <v>130</v>
+      </c>
+      <c r="I28" t="s">
         <v>131</v>
       </c>
-      <c r="I28" t="s">
-        <v>132</v>
-      </c>
       <c r="J28" t="s">
-        <v>105</v>
+        <v>104</v>
+      </c>
+      <c r="K28">
+        <v>4</v>
       </c>
       <c r="L28">
         <v>19.989999999999998</v>
@@ -2223,28 +2235,28 @@
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>145</v>
+      </c>
+      <c r="B29" t="s">
         <v>146</v>
       </c>
-      <c r="B29" t="s">
-        <v>147</v>
-      </c>
       <c r="D29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E29" t="s">
         <v>30</v>
       </c>
       <c r="F29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G29" t="s">
         <v>32</v>
       </c>
       <c r="H29" t="s">
+        <v>90</v>
+      </c>
+      <c r="I29" t="s">
         <v>91</v>
-      </c>
-      <c r="I29" t="s">
-        <v>92</v>
       </c>
       <c r="J29" t="s">
         <v>45</v>
@@ -2264,16 +2276,16 @@
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>148</v>
+      </c>
+      <c r="B30" t="s">
         <v>149</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>150</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>151</v>
-      </c>
-      <c r="D30" t="s">
-        <v>152</v>
       </c>
       <c r="E30" t="s">
         <v>40</v>
@@ -2282,7 +2294,7 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H30" t="s">
         <v>43</v>
@@ -2294,7 +2306,7 @@
         <v>45</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L30">
         <v>249</v>
@@ -2303,27 +2315,27 @@
         <v>36</v>
       </c>
       <c r="N30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" t="s">
         <v>155</v>
       </c>
-      <c r="B31" t="s">
-        <v>156</v>
-      </c>
       <c r="C31" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F31" t="s">
         <v>21</v>
@@ -2332,16 +2344,16 @@
         <v>68</v>
       </c>
       <c r="H31" t="s">
+        <v>84</v>
+      </c>
+      <c r="I31" t="s">
         <v>85</v>
-      </c>
-      <c r="I31" t="s">
-        <v>86</v>
       </c>
       <c r="J31" t="s">
         <v>25</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L31">
         <v>9.5</v>
@@ -2355,16 +2367,16 @@
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" t="s">
         <v>157</v>
       </c>
-      <c r="B32" t="s">
-        <v>158</v>
-      </c>
       <c r="E32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G32" t="s">
         <v>32</v>
@@ -2388,21 +2400,21 @@
         <v>36</v>
       </c>
       <c r="O32" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" t="s">
         <v>160</v>
       </c>
-      <c r="B33" t="s">
+      <c r="D33" t="s">
         <v>161</v>
       </c>
-      <c r="D33" t="s">
-        <v>162</v>
-      </c>
       <c r="E33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F33" t="s">
         <v>31</v>
@@ -2411,13 +2423,13 @@
         <v>68</v>
       </c>
       <c r="H33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I33" t="s">
         <v>24</v>
       </c>
       <c r="J33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K33">
         <v>2</v>
@@ -2434,7 +2446,7 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B34">
         <v>45320</v>
@@ -2449,22 +2461,22 @@
         <v>68</v>
       </c>
       <c r="H34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I34" t="s">
         <v>24</v>
       </c>
       <c r="J34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L34" t="s">
         <v>35</v>
       </c>
       <c r="N34" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P34" t="s">
         <v>49</v>
@@ -2472,31 +2484,31 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" t="s">
         <v>164</v>
       </c>
-      <c r="B35" t="s">
+      <c r="E35" t="s">
+        <v>111</v>
+      </c>
+      <c r="F35" t="s">
         <v>165</v>
       </c>
-      <c r="E35" t="s">
-        <v>112</v>
-      </c>
-      <c r="F35" t="s">
-        <v>166</v>
-      </c>
       <c r="G35" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H35" t="s">
+        <v>130</v>
+      </c>
+      <c r="I35" t="s">
         <v>131</v>
       </c>
-      <c r="I35" t="s">
-        <v>132</v>
-      </c>
       <c r="J35" t="s">
-        <v>105</v>
-      </c>
-      <c r="K35" t="s">
-        <v>69</v>
+        <v>104</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
       </c>
       <c r="M35" t="s">
         <v>47</v>
@@ -2510,28 +2522,28 @@
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>166</v>
+      </c>
+      <c r="B36" t="s">
         <v>167</v>
       </c>
-      <c r="B36" t="s">
+      <c r="D36" t="s">
         <v>168</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F36" t="s">
         <v>169</v>
-      </c>
-      <c r="E36" t="s">
-        <v>97</v>
-      </c>
-      <c r="F36" t="s">
-        <v>170</v>
       </c>
       <c r="G36" t="s">
         <v>68</v>
       </c>
       <c r="H36" t="s">
+        <v>73</v>
+      </c>
+      <c r="I36" t="s">
         <v>74</v>
-      </c>
-      <c r="I36" t="s">
-        <v>75</v>
       </c>
       <c r="J36" t="s">
         <v>45</v>
@@ -2551,31 +2563,31 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37" t="s">
         <v>171</v>
       </c>
-      <c r="B37" t="s">
-        <v>172</v>
-      </c>
       <c r="E37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G37" t="s">
         <v>56</v>
       </c>
       <c r="H37" t="s">
+        <v>102</v>
+      </c>
+      <c r="I37" t="s">
         <v>103</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>104</v>
       </c>
-      <c r="J37" t="s">
-        <v>105</v>
-      </c>
       <c r="K37">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L37">
         <v>249</v>
@@ -2584,36 +2596,36 @@
         <v>0.1</v>
       </c>
       <c r="N37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" t="s">
         <v>173</v>
-      </c>
-      <c r="B39" t="s">
-        <v>174</v>
       </c>
       <c r="E39" t="s">
         <v>30</v>
       </c>
       <c r="F39" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G39" t="s">
         <v>42</v>
       </c>
       <c r="H39" t="s">
+        <v>116</v>
+      </c>
+      <c r="I39" t="s">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s">
         <v>117</v>
-      </c>
-      <c r="I39" t="s">
-        <v>75</v>
-      </c>
-      <c r="J39" t="s">
-        <v>118</v>
       </c>
       <c r="K39">
         <v>4</v>
@@ -2625,7 +2637,7 @@
         <v>0.2</v>
       </c>
       <c r="N39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P39" t="s">
         <v>26</v>
@@ -2633,31 +2645,31 @@
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>175</v>
+      </c>
+      <c r="B40" t="s">
         <v>176</v>
       </c>
-      <c r="B40" t="s">
+      <c r="D40" t="s">
         <v>177</v>
-      </c>
-      <c r="D40" t="s">
-        <v>178</v>
       </c>
       <c r="E40" t="s">
         <v>20</v>
       </c>
       <c r="F40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H40" t="s">
+        <v>102</v>
+      </c>
+      <c r="I40" t="s">
         <v>103</v>
       </c>
-      <c r="I40" t="s">
+      <c r="J40" t="s">
         <v>104</v>
-      </c>
-      <c r="J40" t="s">
-        <v>105</v>
       </c>
       <c r="K40">
         <v>5</v>
@@ -2674,10 +2686,10 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" t="s">
         <v>179</v>
-      </c>
-      <c r="B41" t="s">
-        <v>180</v>
       </c>
       <c r="D41" t="s">
         <v>19</v>
@@ -2686,22 +2698,22 @@
         <v>66</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H41" t="s">
+        <v>73</v>
+      </c>
+      <c r="I41" t="s">
         <v>74</v>
-      </c>
-      <c r="I41" t="s">
-        <v>75</v>
       </c>
       <c r="J41" t="s">
         <v>45</v>
       </c>
-      <c r="K41" t="s">
-        <v>69</v>
+      <c r="K41">
+        <v>2</v>
       </c>
       <c r="L41" t="s">
         <v>35</v>
@@ -2715,28 +2727,28 @@
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>180</v>
+      </c>
+      <c r="B42" t="s">
+        <v>71</v>
+      </c>
+      <c r="D42" t="s">
         <v>181</v>
-      </c>
-      <c r="B42" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" t="s">
-        <v>182</v>
       </c>
       <c r="E42" t="s">
         <v>40</v>
       </c>
       <c r="F42" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G42" t="s">
+        <v>83</v>
+      </c>
+      <c r="H42" t="s">
         <v>84</v>
       </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>85</v>
-      </c>
-      <c r="I42" t="s">
-        <v>86</v>
       </c>
       <c r="J42" t="s">
         <v>25</v>
@@ -2754,36 +2766,36 @@
         <v>980</v>
       </c>
       <c r="P42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B43" t="s">
+        <v>77</v>
+      </c>
+      <c r="E43" t="s">
         <v>78</v>
       </c>
-      <c r="E43" t="s">
-        <v>79</v>
-      </c>
       <c r="F43" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G43" t="s">
         <v>32</v>
       </c>
       <c r="H43" t="s">
+        <v>102</v>
+      </c>
+      <c r="I43" t="s">
         <v>103</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>104</v>
       </c>
-      <c r="J43" t="s">
-        <v>105</v>
-      </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
         <v>19.989999999999998</v>
@@ -2792,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P43" t="s">
         <v>26</v>
@@ -2800,31 +2812,31 @@
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
+        <v>184</v>
+      </c>
+      <c r="B44" t="s">
         <v>185</v>
       </c>
-      <c r="B44" t="s">
+      <c r="E44" t="s">
+        <v>82</v>
+      </c>
+      <c r="F44" t="s">
         <v>186</v>
-      </c>
-      <c r="E44" t="s">
-        <v>83</v>
-      </c>
-      <c r="F44" t="s">
-        <v>187</v>
       </c>
       <c r="G44" t="s">
         <v>22</v>
       </c>
       <c r="H44" t="s">
+        <v>73</v>
+      </c>
+      <c r="I44" t="s">
         <v>74</v>
-      </c>
-      <c r="I44" t="s">
-        <v>75</v>
       </c>
       <c r="J44" t="s">
         <v>45</v>
       </c>
       <c r="K44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L44" t="s">
         <v>46</v>
@@ -2833,10 +2845,10 @@
         <v>47</v>
       </c>
       <c r="N44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O44" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P44" t="s">
         <v>63</v>
@@ -2844,10 +2856,10 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>188</v>
+      </c>
+      <c r="B45" t="s">
         <v>189</v>
-      </c>
-      <c r="B45" t="s">
-        <v>190</v>
       </c>
       <c r="D45" t="s">
         <v>53</v>
@@ -2856,7 +2868,7 @@
         <v>61</v>
       </c>
       <c r="F45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G45" t="s">
         <v>68</v>
@@ -2877,7 +2889,7 @@
         <v>48</v>
       </c>
       <c r="O45" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P45" t="s">
         <v>49</v>
@@ -2885,19 +2897,19 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B46">
         <v>45303</v>
       </c>
       <c r="C46" t="s">
+        <v>192</v>
+      </c>
+      <c r="D46" t="s">
         <v>193</v>
       </c>
-      <c r="D46" t="s">
-        <v>194</v>
-      </c>
       <c r="E46" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F46" t="s">
         <v>41</v>
@@ -2906,13 +2918,13 @@
         <v>56</v>
       </c>
       <c r="H46" t="s">
+        <v>102</v>
+      </c>
+      <c r="I46" t="s">
         <v>103</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>104</v>
-      </c>
-      <c r="J46" t="s">
-        <v>105</v>
       </c>
       <c r="K46">
         <v>4</v>
@@ -2924,36 +2936,36 @@
         <v>36</v>
       </c>
       <c r="N46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>194</v>
+      </c>
+      <c r="B47" t="s">
         <v>195</v>
       </c>
-      <c r="B47" t="s">
-        <v>196</v>
-      </c>
       <c r="D47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F47" t="s">
         <v>41</v>
       </c>
       <c r="G47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H47" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I47" t="s">
         <v>24</v>
       </c>
       <c r="J47" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K47">
         <v>2</v>
@@ -2965,80 +2977,80 @@
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O47" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B48">
         <v>45305</v>
       </c>
       <c r="D48" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E48" t="s">
+        <v>82</v>
+      </c>
+      <c r="F48" t="s">
+        <v>169</v>
+      </c>
+      <c r="G48" t="s">
         <v>83</v>
       </c>
-      <c r="F48" t="s">
-        <v>170</v>
-      </c>
-      <c r="G48" t="s">
-        <v>84</v>
-      </c>
       <c r="H48" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I48" t="s">
         <v>24</v>
       </c>
       <c r="J48" t="s">
-        <v>114</v>
-      </c>
-      <c r="K48" t="s">
-        <v>69</v>
+        <v>113</v>
+      </c>
+      <c r="K48">
+        <v>2</v>
       </c>
       <c r="M48" t="s">
         <v>47</v>
       </c>
       <c r="P48" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B49">
         <v>45306</v>
       </c>
       <c r="E49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G49" t="s">
         <v>42</v>
       </c>
       <c r="H49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I49" t="s">
         <v>24</v>
       </c>
       <c r="J49" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M49" t="s">
         <v>47</v>
@@ -3047,24 +3059,24 @@
         <v>980</v>
       </c>
       <c r="P49" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>199</v>
+      </c>
+      <c r="B50" t="s">
         <v>200</v>
       </c>
-      <c r="B50" t="s">
+      <c r="D50" t="s">
         <v>201</v>
       </c>
-      <c r="D50" t="s">
-        <v>202</v>
-      </c>
       <c r="E50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G50" t="s">
         <v>42</v>
@@ -3078,11 +3090,14 @@
       <c r="J50" t="s">
         <v>45</v>
       </c>
+      <c r="K50">
+        <v>3</v>
+      </c>
       <c r="L50">
         <v>249</v>
       </c>
       <c r="N50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P50" t="s">
         <v>63</v>
@@ -3090,34 +3105,34 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E51" t="s">
+        <v>101</v>
+      </c>
+      <c r="F51" t="s">
+        <v>169</v>
+      </c>
+      <c r="G51" t="s">
+        <v>152</v>
+      </c>
+      <c r="H51" t="s">
         <v>102</v>
       </c>
-      <c r="F51" t="s">
-        <v>170</v>
-      </c>
-      <c r="G51" t="s">
-        <v>153</v>
-      </c>
-      <c r="H51" t="s">
+      <c r="I51" t="s">
         <v>103</v>
       </c>
-      <c r="I51" t="s">
+      <c r="J51" t="s">
         <v>104</v>
       </c>
-      <c r="J51" t="s">
-        <v>105</v>
-      </c>
-      <c r="K51" t="s">
-        <v>69</v>
+      <c r="K51">
+        <v>5</v>
       </c>
       <c r="L51">
         <v>9.5</v>
@@ -3126,36 +3141,36 @@
         <v>47</v>
       </c>
       <c r="P51" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" t="s">
         <v>204</v>
       </c>
-      <c r="B52" t="s">
+      <c r="D52" t="s">
+        <v>201</v>
+      </c>
+      <c r="E52" t="s">
+        <v>78</v>
+      </c>
+      <c r="F52" t="s">
+        <v>186</v>
+      </c>
+      <c r="G52" t="s">
         <v>205</v>
       </c>
-      <c r="D52" t="s">
-        <v>202</v>
-      </c>
-      <c r="E52" t="s">
-        <v>79</v>
-      </c>
-      <c r="F52" t="s">
-        <v>187</v>
-      </c>
-      <c r="G52" t="s">
-        <v>206</v>
-      </c>
       <c r="H52" t="s">
+        <v>130</v>
+      </c>
+      <c r="I52" t="s">
         <v>131</v>
       </c>
-      <c r="I52" t="s">
-        <v>132</v>
-      </c>
       <c r="J52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K52">
         <v>5</v>
@@ -3164,36 +3179,36 @@
         <v>249</v>
       </c>
       <c r="N52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P52" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>206</v>
+      </c>
+      <c r="B53" t="s">
         <v>207</v>
       </c>
-      <c r="B53" t="s">
-        <v>208</v>
-      </c>
       <c r="C53" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E53" t="s">
         <v>40</v>
       </c>
       <c r="F53" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s">
+        <v>90</v>
+      </c>
+      <c r="I53" t="s">
         <v>91</v>
-      </c>
-      <c r="I53" t="s">
-        <v>92</v>
       </c>
       <c r="J53" t="s">
         <v>45</v>
@@ -3208,10 +3223,10 @@
         <v>0</v>
       </c>
       <c r="N53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O53" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P53" t="s">
         <v>49</v>
@@ -3219,13 +3234,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>209</v>
+      </c>
+      <c r="B54" t="s">
         <v>210</v>
       </c>
-      <c r="B54" t="s">
+      <c r="D54" t="s">
         <v>211</v>
-      </c>
-      <c r="D54" t="s">
-        <v>212</v>
       </c>
       <c r="E54" t="s">
         <v>61</v>
@@ -3237,16 +3252,16 @@
         <v>32</v>
       </c>
       <c r="H54" t="s">
+        <v>73</v>
+      </c>
+      <c r="I54" t="s">
         <v>74</v>
-      </c>
-      <c r="I54" t="s">
-        <v>75</v>
       </c>
       <c r="J54" t="s">
         <v>45</v>
       </c>
       <c r="K54" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -3257,31 +3272,31 @@
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>212</v>
+      </c>
+      <c r="B55" t="s">
         <v>213</v>
       </c>
-      <c r="B55" t="s">
-        <v>214</v>
-      </c>
       <c r="D55" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E55" t="s">
         <v>30</v>
       </c>
       <c r="F55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G55" t="s">
         <v>22</v>
       </c>
       <c r="H55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I55" t="s">
         <v>24</v>
       </c>
       <c r="J55" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K55">
         <v>4</v>
@@ -3293,39 +3308,39 @@
         <v>0.2</v>
       </c>
       <c r="N55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B56" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C56">
         <v>45313</v>
       </c>
       <c r="D56" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E56" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F56" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G56" t="s">
         <v>56</v>
       </c>
       <c r="H56" t="s">
+        <v>130</v>
+      </c>
+      <c r="I56" t="s">
         <v>131</v>
       </c>
-      <c r="I56" t="s">
-        <v>132</v>
-      </c>
       <c r="J56" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K56">
         <v>3</v>
@@ -3345,28 +3360,28 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B57">
         <v>45314</v>
       </c>
       <c r="D57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E57" t="s">
         <v>54</v>
       </c>
       <c r="F57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G57" t="s">
         <v>42</v>
       </c>
       <c r="H57" t="s">
+        <v>84</v>
+      </c>
+      <c r="I57" t="s">
         <v>85</v>
-      </c>
-      <c r="I57" t="s">
-        <v>86</v>
       </c>
       <c r="J57" t="s">
         <v>25</v>
@@ -3384,15 +3399,15 @@
         <v>980</v>
       </c>
       <c r="O57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>218</v>
+      </c>
+      <c r="B58" t="s">
         <v>219</v>
-      </c>
-      <c r="B58" t="s">
-        <v>220</v>
       </c>
       <c r="D58" t="s">
         <v>37</v>
@@ -3404,19 +3419,19 @@
         <v>21</v>
       </c>
       <c r="G58" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H58" t="s">
+        <v>90</v>
+      </c>
+      <c r="I58" t="s">
         <v>91</v>
-      </c>
-      <c r="I58" t="s">
-        <v>92</v>
       </c>
       <c r="J58" t="s">
         <v>45</v>
       </c>
-      <c r="K58" t="s">
-        <v>69</v>
+      <c r="K58">
+        <v>2</v>
       </c>
       <c r="L58" t="s">
         <v>46</v>
@@ -3425,7 +3440,7 @@
         <v>47</v>
       </c>
       <c r="O58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P58" t="s">
         <v>63</v>
@@ -3433,28 +3448,28 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E59" t="s">
         <v>66</v>
       </c>
       <c r="F59" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G59" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H59" t="s">
+        <v>130</v>
+      </c>
+      <c r="I59" t="s">
         <v>131</v>
       </c>
-      <c r="I59" t="s">
-        <v>132</v>
-      </c>
       <c r="J59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K59">
         <v>1</v>
@@ -3466,27 +3481,27 @@
         <v>0.1</v>
       </c>
       <c r="N59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G60" t="s">
         <v>42</v>
@@ -3507,24 +3522,24 @@
         <v>36</v>
       </c>
       <c r="N60" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P60" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>224</v>
+      </c>
+      <c r="B61" t="s">
         <v>225</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>226</v>
       </c>
-      <c r="C61" t="s">
-        <v>227</v>
-      </c>
       <c r="E61" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F61" t="s">
         <v>67</v>
@@ -3533,13 +3548,13 @@
         <v>56</v>
       </c>
       <c r="H61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I61" t="s">
         <v>24</v>
       </c>
       <c r="J61" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K61">
         <v>2</v>
@@ -3556,31 +3571,31 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
+        <v>227</v>
+      </c>
+      <c r="B62" t="s">
         <v>228</v>
-      </c>
-      <c r="B62" t="s">
-        <v>229</v>
       </c>
       <c r="E62" t="s">
         <v>30</v>
       </c>
       <c r="F62" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G62" t="s">
         <v>42</v>
       </c>
       <c r="H62" t="s">
+        <v>90</v>
+      </c>
+      <c r="I62" t="s">
         <v>91</v>
-      </c>
-      <c r="I62" t="s">
-        <v>92</v>
       </c>
       <c r="J62" t="s">
         <v>45</v>
       </c>
-      <c r="K62" t="s">
-        <v>69</v>
+      <c r="K62">
+        <v>4</v>
       </c>
       <c r="L62">
         <v>19.989999999999998</v>
@@ -3589,7 +3604,7 @@
         <v>0.1</v>
       </c>
       <c r="O62" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P62" t="s">
         <v>49</v>
@@ -3597,34 +3612,34 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>229</v>
+      </c>
+      <c r="B63" t="s">
         <v>230</v>
-      </c>
-      <c r="B63" t="s">
-        <v>231</v>
       </c>
       <c r="C63">
         <v>45320</v>
       </c>
       <c r="D63" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E63" t="s">
+        <v>82</v>
+      </c>
+      <c r="F63" t="s">
+        <v>147</v>
+      </c>
+      <c r="G63" t="s">
         <v>83</v>
       </c>
-      <c r="F63" t="s">
-        <v>148</v>
-      </c>
-      <c r="G63" t="s">
-        <v>84</v>
-      </c>
       <c r="H63" t="s">
+        <v>130</v>
+      </c>
+      <c r="I63" t="s">
         <v>131</v>
       </c>
-      <c r="I63" t="s">
-        <v>132</v>
-      </c>
       <c r="J63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K63">
         <v>1</v>
@@ -3641,13 +3656,13 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>231</v>
+      </c>
+      <c r="B64" t="s">
         <v>232</v>
       </c>
-      <c r="B64" t="s">
-        <v>233</v>
-      </c>
       <c r="E64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F64" t="s">
         <v>21</v>
@@ -3656,19 +3671,19 @@
         <v>68</v>
       </c>
       <c r="H64" t="s">
+        <v>102</v>
+      </c>
+      <c r="I64" t="s">
         <v>103</v>
       </c>
-      <c r="I64" t="s">
+      <c r="J64" t="s">
         <v>104</v>
       </c>
-      <c r="J64" t="s">
-        <v>105</v>
-      </c>
-      <c r="K64" t="s">
-        <v>69</v>
+      <c r="K64">
+        <v>3</v>
       </c>
       <c r="L64" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M64" t="s">
         <v>47</v>
@@ -3682,13 +3697,13 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" t="s">
         <v>234</v>
       </c>
-      <c r="B65" t="s">
-        <v>235</v>
-      </c>
       <c r="E65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F65" t="s">
         <v>31</v>
@@ -3697,10 +3712,10 @@
         <v>42</v>
       </c>
       <c r="H65" t="s">
+        <v>73</v>
+      </c>
+      <c r="I65" t="s">
         <v>74</v>
-      </c>
-      <c r="I65" t="s">
-        <v>75</v>
       </c>
       <c r="J65" t="s">
         <v>45</v>
@@ -3709,21 +3724,21 @@
         <v>3</v>
       </c>
       <c r="N65" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B66" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F66" t="s">
         <v>67</v>
@@ -3732,10 +3747,10 @@
         <v>22</v>
       </c>
       <c r="H66" t="s">
+        <v>90</v>
+      </c>
+      <c r="I66" t="s">
         <v>91</v>
-      </c>
-      <c r="I66" t="s">
-        <v>92</v>
       </c>
       <c r="J66" t="s">
         <v>45</v>
@@ -3747,10 +3762,10 @@
         <v>9.5</v>
       </c>
       <c r="N66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O66" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P66" t="s">
         <v>63</v>
@@ -3758,86 +3773,86 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B67" t="s">
         <v>51</v>
       </c>
       <c r="D67" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E67" t="s">
         <v>20</v>
       </c>
       <c r="F67" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G67" t="s">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s">
         <v>84</v>
       </c>
-      <c r="H67" t="s">
+      <c r="I67" t="s">
         <v>85</v>
-      </c>
-      <c r="I67" t="s">
-        <v>86</v>
       </c>
       <c r="J67" t="s">
         <v>25</v>
       </c>
-      <c r="K67" t="s">
-        <v>69</v>
+      <c r="K67">
+        <v>2</v>
       </c>
       <c r="L67">
         <v>19.989999999999998</v>
       </c>
       <c r="N67" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B68">
         <v>45297</v>
       </c>
       <c r="D68" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E68" t="s">
         <v>54</v>
       </c>
       <c r="F68" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G68" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H68" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I68" t="s">
         <v>24</v>
       </c>
       <c r="J68" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K68">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L68">
         <v>9.5</v>
       </c>
       <c r="N68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
+        <v>239</v>
+      </c>
+      <c r="B69" t="s">
         <v>240</v>
-      </c>
-      <c r="B69" t="s">
-        <v>241</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -3846,7 +3861,7 @@
         <v>40</v>
       </c>
       <c r="F69" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G69" t="s">
         <v>56</v>
@@ -3860,31 +3875,31 @@
       <c r="J69" t="s">
         <v>25</v>
       </c>
-      <c r="K69" t="s">
-        <v>69</v>
+      <c r="K69">
+        <v>4</v>
       </c>
       <c r="L69" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P69" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>241</v>
+      </c>
+      <c r="B70" t="s">
         <v>242</v>
       </c>
-      <c r="B70" t="s">
+      <c r="E70" t="s">
+        <v>101</v>
+      </c>
+      <c r="F70" t="s">
         <v>243</v>
       </c>
-      <c r="E70" t="s">
-        <v>102</v>
-      </c>
-      <c r="F70" t="s">
-        <v>244</v>
-      </c>
       <c r="G70" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H70" t="s">
         <v>43</v>
@@ -3899,13 +3914,13 @@
         <v>3</v>
       </c>
       <c r="L70" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M70">
         <v>0</v>
       </c>
       <c r="N70" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P70" t="s">
         <v>49</v>
@@ -3913,28 +3928,28 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B71">
         <v>45300</v>
       </c>
       <c r="E71" t="s">
+        <v>82</v>
+      </c>
+      <c r="F71" t="s">
+        <v>124</v>
+      </c>
+      <c r="G71" t="s">
         <v>83</v>
       </c>
-      <c r="F71" t="s">
-        <v>125</v>
-      </c>
-      <c r="G71" t="s">
-        <v>84</v>
-      </c>
       <c r="H71" t="s">
+        <v>102</v>
+      </c>
+      <c r="I71" t="s">
         <v>103</v>
       </c>
-      <c r="I71" t="s">
+      <c r="J71" t="s">
         <v>104</v>
-      </c>
-      <c r="J71" t="s">
-        <v>105</v>
       </c>
       <c r="K71">
         <v>3</v>
@@ -3951,28 +3966,28 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>245</v>
+      </c>
+      <c r="B72" t="s">
         <v>246</v>
       </c>
-      <c r="B72" t="s">
-        <v>247</v>
-      </c>
       <c r="D72" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E72" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F72" t="s">
         <v>55</v>
       </c>
       <c r="G72" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H72" t="s">
+        <v>84</v>
+      </c>
+      <c r="I72" t="s">
         <v>85</v>
-      </c>
-      <c r="I72" t="s">
-        <v>86</v>
       </c>
       <c r="J72" t="s">
         <v>25</v>
@@ -3984,33 +3999,33 @@
         <v>57</v>
       </c>
       <c r="P72" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B73" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F73" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G73" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H73" t="s">
+        <v>130</v>
+      </c>
+      <c r="I73" t="s">
         <v>131</v>
       </c>
-      <c r="I73" t="s">
-        <v>132</v>
-      </c>
       <c r="J73" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K73">
         <v>3</v>
@@ -4019,33 +4034,33 @@
         <v>46</v>
       </c>
       <c r="N73" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O73" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P73" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>248</v>
+      </c>
+      <c r="B74" t="s">
         <v>249</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>250</v>
-      </c>
-      <c r="C74" t="s">
-        <v>251</v>
       </c>
       <c r="E74" t="s">
         <v>61</v>
       </c>
       <c r="F74" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G74" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H74" t="s">
         <v>23</v>
@@ -4066,15 +4081,15 @@
         <v>0.2</v>
       </c>
       <c r="N74" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P74" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B75">
         <v>45304</v>
@@ -4083,22 +4098,22 @@
         <v>53</v>
       </c>
       <c r="E75" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H75" t="s">
+        <v>130</v>
+      </c>
+      <c r="I75" t="s">
         <v>131</v>
       </c>
-      <c r="I75" t="s">
-        <v>132</v>
-      </c>
       <c r="J75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K75">
         <v>2</v>
@@ -4110,45 +4125,45 @@
         <v>0.2</v>
       </c>
       <c r="N75" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O75" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="P75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B76">
         <v>45305</v>
       </c>
       <c r="C76" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E76" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F76" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G76" t="s">
         <v>68</v>
       </c>
       <c r="H76" t="s">
+        <v>90</v>
+      </c>
+      <c r="I76" t="s">
         <v>91</v>
-      </c>
-      <c r="I76" t="s">
-        <v>92</v>
       </c>
       <c r="J76" t="s">
         <v>45</v>
       </c>
-      <c r="K76" t="s">
-        <v>69</v>
+      <c r="K76">
+        <v>3</v>
       </c>
       <c r="L76">
         <v>19.989999999999998</v>
@@ -4159,60 +4174,60 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B77" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D77" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E77" t="s">
         <v>20</v>
       </c>
       <c r="F77" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G77" t="s">
         <v>56</v>
       </c>
       <c r="H77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I77" t="s">
         <v>24</v>
       </c>
       <c r="J77" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K77">
         <v>5</v>
       </c>
       <c r="L77" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M77" t="s">
         <v>47</v>
       </c>
       <c r="N77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P77" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
+      <c r="A79" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4231,17 +4246,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
